--- a/output/pdf_financials_xlsx/PUR.xlsx
+++ b/output/pdf_financials_xlsx/PUR.xlsx
@@ -2279,13 +2279,13 @@
         <v>0</v>
       </c>
       <c r="C91" s="3" t="n">
-        <v>0</v>
+        <v>0.137035</v>
       </c>
       <c r="D91" s="3" t="n">
-        <v>0</v>
+        <v>-0.163679</v>
       </c>
       <c r="E91" s="3" t="n">
-        <v>0</v>
+        <v>-0.068063</v>
       </c>
     </row>
     <row r="92">
@@ -2295,16 +2295,16 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0.1367</v>
+        <v>0.35213</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0.169716</v>
+        <v>1.378602</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0.169716</v>
+        <v>4.056435</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0.169716</v>
+        <v>7.189779</v>
       </c>
     </row>
     <row r="93">
@@ -3680,7 +3680,11 @@
           <t>Warrant reserve 7</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr"/>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E15" t="inlineStr">
         <is>
           <t>-</t>
@@ -3812,7 +3816,11 @@
           <t>Foreign currency translation reserve</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr"/>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>GainsLossesNotAffectingRetainedEarnings</t>
+        </is>
+      </c>
       <c r="E19" t="inlineStr">
         <is>
           <t>-</t>
@@ -4240,7 +4248,11 @@
           <t>Warrant reserve 6</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr"/>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E31" s="5" t="n">
         <v>0.21543</v>
       </c>
@@ -8720,7 +8732,7 @@
         </is>
       </c>
       <c r="E159" s="5" t="n">
-        <v>0.452804</v>
+        <v>-0.452804</v>
       </c>
       <c r="F159" s="5" t="n">
         <v>-11.685848</v>

--- a/output/pdf_financials_xlsx/PUR.xlsx
+++ b/output/pdf_financials_xlsx/PUR.xlsx
@@ -674,7 +674,7 @@
         <v>0</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>-0.018629</v>
       </c>
       <c r="D12" s="1" t="inlineStr">
         <is>
@@ -1023,7 +1023,7 @@
         <v>-0.452804</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-11.822883</v>
+        <v>-11.804254</v>
       </c>
       <c r="D27" s="1" t="inlineStr">
         <is>
@@ -1069,7 +1069,7 @@
         <v>-0.452804</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-11.822883</v>
+        <v>-11.804254</v>
       </c>
       <c r="D29" s="1" t="inlineStr">
         <is>
@@ -3398,7 +3398,11 @@
           <t>Reclamation deposits 13</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr"/>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E7" t="inlineStr">
         <is>
           <t>-</t>
@@ -4952,7 +4956,11 @@
           <t>Reclamation deposits 13</t>
         </is>
       </c>
-      <c r="D51" t="inlineStr"/>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>ChangeInRestrictedCash</t>
+        </is>
+      </c>
       <c r="E51" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/PUR.xlsx
+++ b/output/pdf_financials_xlsx/PUR.xlsx
@@ -2628,13 +2628,13 @@
         <v>0</v>
       </c>
       <c r="C110" s="3" t="n">
-        <v>0</v>
+        <v>0.014769</v>
       </c>
       <c r="D110" s="3" t="n">
-        <v>0</v>
+        <v>0.040896</v>
       </c>
       <c r="E110" s="3" t="n">
-        <v>0</v>
+        <v>0.043851</v>
       </c>
     </row>
     <row r="111">
@@ -4684,7 +4684,11 @@
           <t>Accretion expense 10</t>
         </is>
       </c>
-      <c r="D43" t="inlineStr"/>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E43" t="inlineStr">
         <is>
           <t>-</t>
@@ -6110,7 +6114,11 @@
           <t>Accretion expense</t>
         </is>
       </c>
-      <c r="D84" t="inlineStr"/>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E84" t="inlineStr">
         <is>
           <t>-</t>
@@ -6616,7 +6624,11 @@
           <t>Payment of share issue costs related to private placement 6</t>
         </is>
       </c>
-      <c r="D98" t="inlineStr"/>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E98" s="5" t="n">
         <v>-0.06432499999999999</v>
       </c>
